--- a/SkillHub_Шаблон_импорта_кейсов.xlsx
+++ b/SkillHub_Шаблон_импорта_кейсов.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R41e142e0f26a43e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кейсы" sheetId="2" r:id="Rd58d3efda687438d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Диалоги" sheetId="3" r:id="Rab3908ecf553454c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шаги диалогов" sheetId="4" r:id="Rc442d3b4818e4712"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сотрудники" sheetId="5" r:id="R1cc1e8e7c89c415a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Назначения" sheetId="6" r:id="R1d25648bcbcb4791"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R213352bbaf1f4dc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кейсы" sheetId="2" r:id="Rff01cd7bf65b4cfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Диалоги" sheetId="3" r:id="R520c9dc856ea4b10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шаги диалогов" sheetId="4" r:id="Rbd89bac2582e4c70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сотрудники" sheetId="5" r:id="R3d6b7a41881946a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Назначения" sheetId="6" r:id="R313f6b8396564b68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Темы для аналитики" sheetId="7" r:id="Re9ef4dde32d64ff4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -41,7 +42,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -63,6 +64,16 @@
         <x:fgColor rgb="FF1E3A8A"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF172554"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAFE"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -71,7 +82,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="40">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -133,6 +144,26 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -424,8 +455,8 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="85" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="78" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -514,9 +545,48 @@
         <x:v>Не используйте реальные клиентские персональные данные и банковские реквизиты в учебных кейсах.</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="34" t="str">
+        <x:v>АДАПТИВНАЯ АНАЛИТИКА</x:v>
+      </x:c>
+      <x:c r="B12" s="34" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="39" t="str">
+        <x:v>Что считается пробелом</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="str">
+        <x:v>Минимум 2 попытки по одной теме и средний результат последних 3 попыток ниже 75%.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="39" t="str">
+        <x:v>Закрепить</x:v>
+      </x:c>
+      <x:c r="B14" s="16" t="str">
+        <x:v>75–89% — тема требует закрепления, но не считается критическим пробелом.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="39" t="str">
+        <x:v>Сильная тема</x:v>
+      </x:c>
+      <x:c r="B15" s="16" t="str">
+        <x:v>90% и выше.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="39" t="str">
+        <x:v>Важно</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="str">
+        <x:v>Поле «Тема» — ключ аналитики. Например, все кредитные кейсы должны иметь одинаковую тему «Кредиты».</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:B1"/>
+    <x:mergeCell ref="A12:B12"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4263,7 +4333,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R402a3108aa7a4496"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe55e9bc01a44af1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6328,7 +6398,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R577ec8677d0c413e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2de495a78b94773"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8610,7 +8680,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce4a17231ce7402d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70c42c2f431e4251"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10217,7 +10287,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra45844217ec54da3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R884ab1ce4a064d05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12688,7 +12758,214 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6e9012e68954cc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R486f97e6fe354487"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="35" t="str">
+        <x:v>Раздел</x:v>
+      </x:c>
+      <x:c r="B1" s="35" t="str">
+        <x:v>Тема</x:v>
+      </x:c>
+      <x:c r="C1" s="35" t="str">
+        <x:v>Примеры кейсов внутри темы</x:v>
+      </x:c>
+      <x:c r="D1" s="35" t="str">
+        <x:v>Как использовать</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="44" customHeight="1">
+      <x:c r="A2" s="16" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="B2" s="16" t="str">
+        <x:v>Кредиты</x:v>
+      </x:c>
+      <x:c r="C2" s="16" t="str">
+        <x:v>Овердрафт; оборотный кредит; КДС; погашение; комиссия; просрочка</x:v>
+      </x:c>
+      <x:c r="D2" s="16" t="str">
+        <x:v>Во всех кейсах по кредитам пишите тему одинаково: «Кредиты»</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="44" customHeight="1">
+      <x:c r="A3" s="16" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="B3" s="16" t="str">
+        <x:v>Тарифы</x:v>
+      </x:c>
+      <x:c r="C3" s="16" t="str">
+        <x:v>Смена тарифа; дата смены; условия тарифа; где посмотреть ИУ</x:v>
+      </x:c>
+      <x:c r="D3" s="16" t="str">
+        <x:v>Одинаковая тема позволяет SkillHub собрать общий результат</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="44" customHeight="1">
+      <x:c r="A4" s="16" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Онлайн-бухгалтерия</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>Декларация; взносы; уменьшение налога; сроки оплаты</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Не меняйте написание темы между кейсами</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="44" customHeight="1">
+      <x:c r="A5" s="16" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="B5" s="16" t="str">
+        <x:v>Госорганы</x:v>
+      </x:c>
+      <x:c r="C5" s="16" t="str">
+        <x:v>Требования; блокировка; арест; документы; очередность платежей</x:v>
+      </x:c>
+      <x:c r="D5" s="16" t="str">
+        <x:v>Механика ответа берётся только из актуальной базы знаний банка</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="44" customHeight="1">
+      <x:c r="A6" s="16" t="str">
+        <x:v>soft</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="str">
+        <x:v>Присоединение</x:v>
+      </x:c>
+      <x:c r="C6" s="16" t="str">
+        <x:v>Негатив; повторное обращение; эмоциональная реакция</x:v>
+      </x:c>
+      <x:c r="D6" s="16" t="str">
+        <x:v>Можно создавать несколько кейсов одной темы</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="44" customHeight="1">
+      <x:c r="A7" s="16" t="str">
+        <x:v>soft</x:v>
+      </x:c>
+      <x:c r="B7" s="16" t="str">
+        <x:v>Факт и ограничение</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="str">
+        <x:v>Объяснение факта без обещаний и догадок</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="str">
+        <x:v>Используйте единое название темы</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="44" customHeight="1">
+      <x:c r="A8" s="16" t="str">
+        <x:v>soft</x:v>
+      </x:c>
+      <x:c r="B8" s="16" t="str">
+        <x:v>Поддержка и следующий шаг</x:v>
+      </x:c>
+      <x:c r="C8" s="16" t="str">
+        <x:v>Поддержка клиента; перевод к действию</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="str">
+        <x:v>Используйте единое название темы</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="44" customHeight="1">
+      <x:c r="A9" s="16" t="str">
+        <x:v>needs</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>Выявление потребности</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="str">
+        <x:v>Открытые вопросы; уточнение цели; критерии</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="str">
+        <x:v>Все кейсы диагностики можно объединить одной темой</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="44" customHeight="1">
+      <x:c r="A10" s="16"/>
+      <x:c r="B10" s="16"/>
+      <x:c r="C10" s="16"/>
+      <x:c r="D10" s="16"/>
+    </x:row>
+    <x:row r="11" ht="44" customHeight="1">
+      <x:c r="A11" s="16"/>
+      <x:c r="B11" s="16"/>
+      <x:c r="C11" s="16"/>
+      <x:c r="D11" s="16"/>
+    </x:row>
+    <x:row r="12" ht="44" customHeight="1">
+      <x:c r="A12" s="16"/>
+      <x:c r="B12" s="16"/>
+      <x:c r="C12" s="16"/>
+      <x:c r="D12" s="16"/>
+    </x:row>
+    <x:row r="13" ht="44" customHeight="1">
+      <x:c r="A13" s="16"/>
+      <x:c r="B13" s="16"/>
+      <x:c r="C13" s="16"/>
+      <x:c r="D13" s="16"/>
+    </x:row>
+    <x:row r="14" ht="44" customHeight="1">
+      <x:c r="A14" s="16"/>
+      <x:c r="B14" s="16"/>
+      <x:c r="C14" s="16"/>
+      <x:c r="D14" s="16"/>
+    </x:row>
+    <x:row r="15" ht="44" customHeight="1">
+      <x:c r="A15" s="16"/>
+      <x:c r="B15" s="16"/>
+      <x:c r="C15" s="16"/>
+      <x:c r="D15" s="16"/>
+    </x:row>
+    <x:row r="16" ht="44" customHeight="1">
+      <x:c r="A16" s="16"/>
+      <x:c r="B16" s="16"/>
+      <x:c r="C16" s="16"/>
+      <x:c r="D16" s="16"/>
+    </x:row>
+    <x:row r="17" ht="44" customHeight="1">
+      <x:c r="A17" s="16"/>
+      <x:c r="B17" s="16"/>
+      <x:c r="C17" s="16"/>
+      <x:c r="D17" s="16"/>
+    </x:row>
+    <x:row r="18" ht="44" customHeight="1">
+      <x:c r="A18" s="16"/>
+      <x:c r="B18" s="16"/>
+      <x:c r="C18" s="16"/>
+      <x:c r="D18" s="16"/>
+    </x:row>
+    <x:row r="19" ht="44" customHeight="1">
+      <x:c r="A19" s="16"/>
+      <x:c r="B19" s="16"/>
+      <x:c r="C19" s="16"/>
+      <x:c r="D19" s="16"/>
+    </x:row>
+    <x:row r="20" ht="44" customHeight="1">
+      <x:c r="A20" s="16"/>
+      <x:c r="B20" s="16"/>
+      <x:c r="C20" s="16"/>
+      <x:c r="D20" s="16"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>